--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_928_Colombia_Pacific.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_928_Colombia_Pacific.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R5470b2ad96d54fcb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Re6828e74c9dd4ee5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R64b1661c3a2a4655"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rec1a37e8bbe94b0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R9a6066df15b84f73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R8ee92bd7312e46a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rf3a5271d0a594e70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R8cc35acc436b4805"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R63de0a6062b14914"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R12448438d3804eb6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R8be4194258224893"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rb0c6cd612bb54d2a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ928CommercialTable" displayName="EEZ928CommercialTable" ref="A1:O10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O10"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ928CommercialTable" displayName="EEZ928CommercialTable" ref="A1:E10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E10"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ928FunctionalTable" displayName="EEZ928FunctionalTable" ref="A1:O18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O18"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ928FunctionalTable" displayName="EEZ928FunctionalTable" ref="A1:E18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E18"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ928ValidationTable" displayName="EEZ928ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ928ValidationTable" displayName="EEZ928ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -6523,7 +6477,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc72d2a373fb248fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e985193b91d4292"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6533,20 +6487,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6554,552 +6498,193 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>2096.1359381176003</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>2.68683649941468</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>48.62241204855945</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>2096.1359381176003</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>67.82301062616521</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$88,A2,'Species'!$U$2:$U$88))</x:f>
-        <x:v>142166.2500048368</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>2.68683649941468</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>48.62241204855945</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>101919.18529294767</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>40247.06471188912</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.394891939100636</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.3948919391006359</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>2826.5009656548</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.191697666956631</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>155.4882826868751</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>2826.5009656548</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>221.18987309705085</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$88,A3,'Species'!$U$2:$U$88))</x:f>
-        <x:v>625193.3899018769</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.191697666956631</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>155.4882826868751</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>439487.781162459</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>185705.60873941792</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.422550106508583</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.4225501065085831</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>142.1471127323</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.9014594232295923</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>797.0020220436456</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>142.1471127323</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>837.0029279038826</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$88,A4,'Species'!$U$2:$U$88))</x:f>
-        <x:v>118977.54955001836</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.9014594232295923</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>797.0020220436456</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>113291.53627530915</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>5686.013274709214</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0501892150256633</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0501892150256632</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>171.4790108462</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.116546208909024</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>130.7814682928072</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>171.4790108462</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>133.77399270732383</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$88,A5,'Species'!$U$2:$U$88))</x:f>
-        <x:v>22939.43194639866</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.116546208909024</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>130.7814682928072</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>22426.276819864248</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>513.1551265344133</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0228818689190478</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.022881868919047775</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>458.87000000000006</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.0031146076230737</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>10.071974269451164</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>458.87000000000006</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>10.202043047427955</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$88,A6,'Species'!$U$2:$U$88))</x:f>
-        <x:v>4681.4114931732665</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.0031146076230737</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>10.071974269451164</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>4621.726833023056</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>59.68466015021022</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0129139307247137</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.012913930724713706</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>12628.364201328799</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.4363515002905762</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>273.11874005026385</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>12628.364201328799</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>534.5615442219752</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$88,A7,'Species'!$U$2:$U$88))</x:f>
-        <x:v>6750637.868459833</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.4363515002905762</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>273.11874005026385</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>3449042.919562778</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>3301594.948897055</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.9572495981916007</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.9572495981916008</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>14297.022331554701</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.8670371002854416</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>736.2699918240023</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>14297.022331554701</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1224.640021868909</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$88,A8,'Species'!$U$2:$U$88))</x:f>
-        <x:v>17508705.74077543</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.8670371002854416</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>736.2699918240023</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>10526468.515161358</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>6982237.225614071</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.6633029126109575</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.6633029126109576</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>608.825904134</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.243686858579017</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1752.6163488250031</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>608.825904134</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1932.6639479524363</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$88,A9,'Species'!$U$2:$U$88))</x:f>
-        <x:v>1176655.875499328</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.243686858579017</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1752.6163488250031</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1067038.2331734125</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>109617.6423259154</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1027307540798312</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.10273075407983118</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>21618.6297385751</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.408533243341434</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>2561.729345750518</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>21618.6297385751</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2595.385242137051</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$88,A10,'Species'!$U$2:$U$88))</x:f>
-        <x:v>56108672.57872299</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.408533243341434</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>2561.729345750518</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>55381078.21622268</x:v>
       </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>727594.36250031</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0131379594969168</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.01313795949691671</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G10">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O10">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54fb23921552404e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06febd874cac459f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7109,20 +6694,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7130,984 +6705,345 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>1498.6799999999998</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>2.8487472308965223</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>70.59065812556567</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>1498.6799999999998</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>262.74505452720996</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$88,A2,'Species'!$U$2:$U$88))</x:f>
-        <x:v>393770.758318839</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>2.8487472308965223</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>70.59065812556567</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>105792.80751962274</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>287977.9507992163</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>3.72209385071666</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>2.72209385071666</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1459.7</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.1309836267726245</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1352.021590006435</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1459.7</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1390.6443135251318</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$88,A3,'Species'!$U$2:$U$88))</x:f>
-        <x:v>2029923.5044526348</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.1309836267726245</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1352.021590006435</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1973545.9149323932</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>56377.5895202416</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0285666470152395</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.028566647015239522</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>23931.6494705913</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.419996664032272</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2630.2477879650937</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>23931.6494705913</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2650.1419639275477</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$88,A4,'Species'!$U$2:$U$88))</x:f>
-        <x:v>63422268.52801848</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.419996664032272</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2630.2477879650937</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>62946168.08237877</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>476100.4456397146</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0075636128479915</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.007563612847991533</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>609.79125</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.109635858992728</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1287.1698513979147</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>609.79125</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1299.9016262967573</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$88,A5,'Species'!$U$2:$U$88))</x:f>
-        <x:v>792668.6375765326</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.109635858992728</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1287.1698513979147</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>784904.9126462487</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>7763.724930283846</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0098912935888107</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.00989129358881068</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>599.695904134</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.253334349880765</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1791.9849168461565</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>599.695904134</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1955.88545040469</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$88,A6,'Species'!$U$2:$U$88))</x:f>
-        <x:v>1172936.4935629764</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.253334349880765</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1791.9849168461565</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>1074646.0149025465</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>98290.47866042983</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0914631211556145</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.09146312115561442</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1334.0409656548002</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.5628574834642572</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>365.4748390065996</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1334.0409656548002</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>368.39591089752133</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$88,A7,'Species'!$U$2:$U$88))</x:f>
-        <x:v>491455.23671700904</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.5628574834642572</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>365.4748390065996</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>487558.4071508968</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>3896.829566112254</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0079925389634523</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.00799253896345224</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>661.5500000000001</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.7000000000000006</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>501.18723362727303</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>661.5500000000001</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>501.18723362727246</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$88,A8,'Species'!$U$2:$U$88))</x:f>
-        <x:v>331560.4144061221</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.7000000000000006</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>501.18723362727303</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>331560.4144061225</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>-4.0745362639427185e-10</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>0.9999999999999988</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>-1.2288970838816394e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>15385.0882761662</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.5499446221756847</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>354.7681490988843</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>15385.0882761662</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>615.005001878661</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$88,A9,'Species'!$U$2:$U$88))</x:f>
-        <x:v>9461906.244186958</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.5499446221756847</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>354.7681490988843</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>5458139.291458427</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>4003766.9527285313</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.7335406333425976</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.7335406333425976</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>996.596431466</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.732718899304191</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>540.4044284852998</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>996.596431466</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>736.2514547420484</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$88,A10,'Species'!$U$2:$U$88))</x:f>
-        <x:v>733745.5724575766</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.732718899304191</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>540.4044284852998</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>538565.124976873</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>195180.4474807036</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.3624082556201258</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.36240825562012574</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>3226.3738374516</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.6477548818253354</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>444.38038596238886</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>3226.3738374516</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>773.3524312528322</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$88,A11,'Species'!$U$2:$U$88))</x:f>
-        <x:v>2495124.051323725</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.6477548818253354</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>444.38038596238886</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1433737.2511456958</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>1061386.800178029</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.7402938016222134</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.7402938016222133</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>458.87000000000006</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>2.0031146076230737</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>10.071974269451164</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>458.87000000000006</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>10.202043047427955</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$88,A12,'Species'!$U$2:$U$88))</x:f>
-        <x:v>4681.4114931732665</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>2.0031146076230737</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>10.071974269451164</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>4621.726833023056</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>59.68466015021022</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0129139307247137</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.012913930724713706</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>1492.46</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>2.8599350736368145</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>72.43276660980837</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>1492.46</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>89.60920439064881</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$88,A13,'Species'!$U$2:$U$88))</x:f>
-        <x:v>133738.15318486773</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>2.8599350736368145</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>72.43276660980837</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>108103.0068544746</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>25635.146330393123</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.2371362932106271</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.23713629321062712</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>281.5657366139</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.03</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>107.1519305237606</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>281.5657366139</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>107.1519305237606</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$88,A14,'Species'!$U$2:$U$88))</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>30170.31224752409</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.03</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>107.1519305237606</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
-        <x:v>30170.31224752409</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>156.8912691696</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.6199999999999997</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>416.8693834703351</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>156.8912691696</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>416.8693834703355</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$88,A15,'Species'!$U$2:$U$88))</x:f>
-        <x:v>65403.16665060961</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.6199999999999997</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>416.8693834703351</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>65403.16665060955</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>5.820766091346741e-11</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0000000000000009</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>8.899823035239062e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>2603.7449489638</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.918180757471353</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>82.82868327946544</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>2603.7449489638</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>298.2552805640699</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$88,A16,'Species'!$U$2:$U$88))</x:f>
-        <x:v>776580.6802704781</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.918180757471353</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>82.82868327946544</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>215664.7657182305</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>560915.9145522476</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>3.6008695147036365</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>2.6008695147036365</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>142.1471127323</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.9014594232295923</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>797.0020220436456</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>142.1471127323</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>837.0029279038826</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$88,A17,'Species'!$U$2:$U$88))</x:f>
-        <x:v>118977.54955001836</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.9014594232295923</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>797.0020220436456</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>113291.53627530915</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>5686.013274709214</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0501892150256633</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.0501892150256632</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>9.13</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.6099999999999994</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>407.3802778041122</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>9.13</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>407.3802778041126</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$88,A18,'Species'!$U$2:$U$88))</x:f>
-        <x:v>3719.3819363515486</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.6099999999999994</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>407.3802778041122</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>3719.381936351545</x:v>
       </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>3.637978807091713e-12</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0000000000000009</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>9.781138020636614e-16</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G18">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O18">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f9ec4b69acf456c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2317e5739a641c0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8282,7 +7218,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -8381,7 +7317,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>82458630.09635389</x:v>
+        <x:v>71105374.39050384</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8395,7 +7331,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>82458630.09635389</x:v>
+        <x:v>75675592.11803311</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8409,7 +7345,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-11353255.70585005</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8423,7 +7359,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-6783037.978320777</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8434,9 +7370,9 @@
         <x:v>EEZ_928</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -8448,47 +7384,19 @@
         <x:v>EEZ_928</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_928</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_928</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raeb0b3e340b54325"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R673eed7d6f434854"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8535,7 +7443,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
